--- a/artfynd/A 62837-2025 artfynd.xlsx
+++ b/artfynd/A 62837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79151900</v>
+        <v>131016223</v>
       </c>
       <c r="B2" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hornberga-Hällberg, Dlr</t>
+          <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477315.0299182539</v>
+        <v>477082</v>
       </c>
       <c r="R2" t="n">
-        <v>6789037.726100092</v>
+        <v>6789158</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sågs längs vägen på 2 platser Hornberga-Hällberg, även unge på minst en av lokalerna</t>
+          <t>Garnlav i äldre tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,26 +775,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131016458</v>
+        <v>131016331</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -835,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477100</v>
+        <v>477092</v>
       </c>
       <c r="R3" t="n">
-        <v>6789140</v>
+        <v>6789185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild</t>
+          <t>Miljöbild, äldre tall med garnlav</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,53 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131022765</v>
+        <v>131016458</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477085</v>
+        <v>477100</v>
       </c>
       <c r="R4" t="n">
-        <v>6789001</v>
+        <v>6789140</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,9 +967,24 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,53 +1011,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131017387</v>
+        <v>131016558</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477188</v>
+        <v>477128</v>
       </c>
       <c r="R5" t="n">
-        <v>6789131</v>
+        <v>6789106</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,11 +1092,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på fem granar inom en radie av 5 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,50 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131017110</v>
+        <v>131016826</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477185</v>
+        <v>477126</v>
       </c>
       <c r="R6" t="n">
-        <v>6789174</v>
+        <v>6789152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,6 +1199,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Garn med miljöbilder för området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,14 +1230,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131016558</v>
+        <v>131016886</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1284,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477128</v>
+        <v>477116</v>
       </c>
       <c r="R7" t="n">
-        <v>6789106</v>
+        <v>6789167</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,14 +1337,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131017563</v>
+        <v>131016935</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1391,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477226</v>
+        <v>477129</v>
       </c>
       <c r="R8" t="n">
-        <v>6789084</v>
+        <v>6789191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,11 +1418,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,14 +1444,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131016886</v>
+        <v>131016952</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1503,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477116</v>
+        <v>477160</v>
       </c>
       <c r="R9" t="n">
-        <v>6789167</v>
+        <v>6789179</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,14 +1551,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131023058</v>
+        <v>131016974</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1604,19 +1580,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477070</v>
+        <v>477179</v>
       </c>
       <c r="R10" t="n">
-        <v>6788943</v>
+        <v>6789184</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,18 +1619,32 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt i området</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1676,14 +1663,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131016935</v>
+        <v>131017116</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1711,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477129</v>
+        <v>477185</v>
       </c>
       <c r="R11" t="n">
-        <v>6789191</v>
+        <v>6789174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,6 +1744,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt i området</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,14 +1775,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131016826</v>
+        <v>131017563</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1818,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477126</v>
+        <v>477226</v>
       </c>
       <c r="R12" t="n">
-        <v>6789152</v>
+        <v>6789084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,7 +1860,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Garn med miljöbilder för området</t>
+          <t>Rikligt i området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,14 +1887,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131016263</v>
+        <v>131017743</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1930,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477082</v>
+        <v>477205</v>
       </c>
       <c r="R13" t="n">
-        <v>6789158</v>
+        <v>6789092</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,50 +1994,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131017558</v>
+        <v>131022711</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477226</v>
+        <v>477096</v>
       </c>
       <c r="R14" t="n">
-        <v>6789084</v>
+        <v>6789012</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,19 +2065,14 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:48</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt i området</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,6 +2081,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2114,42 +2100,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131022979</v>
+        <v>131022789</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2157,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477074</v>
+        <v>477076</v>
       </c>
       <c r="R15" t="n">
-        <v>6788935</v>
+        <v>6788997</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,12 +2176,18 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt i området</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2219,14 +2206,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131017743</v>
+        <v>131022915</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2248,16 +2235,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477205</v>
+        <v>477093</v>
       </c>
       <c r="R16" t="n">
-        <v>6789092</v>
+        <v>6788924</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,27 +2277,18 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2326,14 +2307,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131016952</v>
+        <v>131023058</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2355,16 +2336,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477160</v>
+        <v>477070</v>
       </c>
       <c r="R17" t="n">
-        <v>6789179</v>
+        <v>6788943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,27 +2378,18 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2433,14 +2408,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131022711</v>
+        <v>131023081</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2471,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477096</v>
+        <v>477058</v>
       </c>
       <c r="R18" t="n">
-        <v>6789012</v>
+        <v>6788898</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2486,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt i området</t>
+          <t>Miljöbilder i område med garnlav</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,27 +2514,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131017298</v>
+        <v>131017558</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2579,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477176</v>
+        <v>477226</v>
       </c>
       <c r="R19" t="n">
-        <v>6789136</v>
+        <v>6789084</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,37 +2626,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131022915</v>
+        <v>131022765</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2689,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477093</v>
+        <v>477085</v>
       </c>
       <c r="R20" t="n">
-        <v>6788924</v>
+        <v>6789001</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,7 +2713,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2752,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131022892</v>
+        <v>131017110</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,24 +2760,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477106</v>
+        <v>477185</v>
       </c>
       <c r="R21" t="n">
-        <v>6788935</v>
+        <v>6789174</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,9 +2804,19 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2857,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131016974</v>
+        <v>131017298</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2868,34 +2854,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477179</v>
+        <v>477176</v>
       </c>
       <c r="R22" t="n">
-        <v>6789184</v>
+        <v>6789136</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,11 +2929,6 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt i området</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2969,10 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131022789</v>
+        <v>131017387</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2980,26 +2966,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3007,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477076</v>
+        <v>477188</v>
       </c>
       <c r="R23" t="n">
-        <v>6788997</v>
+        <v>6789131</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,14 +3031,24 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt i området</t>
+          <t>Ringhack på fem granar inom en radie av 5 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3056,7 +3057,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131017116</v>
+        <v>131022847</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,34 +3086,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477185</v>
+        <v>477122</v>
       </c>
       <c r="R24" t="n">
-        <v>6789174</v>
+        <v>6788910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,24 +3151,9 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt i området</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131022847</v>
+        <v>131022892</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477122</v>
+        <v>477106</v>
       </c>
       <c r="R25" t="n">
-        <v>6788910</v>
+        <v>6788935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3292,10 +3285,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131016331</v>
+        <v>131022979</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,34 +3296,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Trossbygget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477092</v>
+        <v>477074</v>
       </c>
       <c r="R26" t="n">
-        <v>6789185</v>
+        <v>6788935</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,24 +3361,9 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbild, äldre tall med garnlav</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3401,6 +3387,116 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>79151900</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hornberga-Hällberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>477315</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6789038</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2019-07-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2019-07-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sågs längs vägen på 2 platser Hornberga-Hällberg, även unge på minst en av lokalerna</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62837-2025 artfynd.xlsx
+++ b/artfynd/A 62837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131016223</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131016331</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131016458</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131016558</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131016826</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131016886</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131016935</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131016952</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131016974</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131017116</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1884,6 +1939,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131017563</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131017743</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2097,6 +2162,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022711</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2203,6 +2273,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022789</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2304,6 +2379,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022915</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2405,6 +2485,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131023058</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2511,6 +2596,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131023081</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2623,6 +2713,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131017558</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2728,6 +2823,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022765</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2840,6 +2940,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131017110</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2952,6 +3057,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131017298</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3072,6 +3182,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131017387</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3177,6 +3292,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022847</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3282,6 +3402,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022892</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3387,6 +3512,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022979</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3497,8 +3627,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79151900</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>